--- a/artfynd/A 10491-2024 artfynd.xlsx
+++ b/artfynd/A 10491-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89594008</v>
+        <v>89594001</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418423.0021088568</v>
+        <v>418435</v>
       </c>
       <c r="R2" t="n">
-        <v>7014271.006423521</v>
+        <v>7014251</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89594001</v>
+        <v>89594008</v>
       </c>
       <c r="B3" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418435.1295503206</v>
+        <v>418423</v>
       </c>
       <c r="R3" t="n">
-        <v>7014250.867639839</v>
+        <v>7014271</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116235504</v>
+        <v>116234104</v>
       </c>
       <c r="B4" t="n">
-        <v>74661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bustadmyren (Bustadmyren), Jmt</t>
+          <t>Bustadmyren, Bustadmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418503</v>
+        <v>418382</v>
       </c>
       <c r="R4" t="n">
-        <v>7014156</v>
+        <v>7014232</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,22 +971,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Edwang Stridbo, Jonny Daborg, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Jonny Daborg, Linnea Edwang Stridbo</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116234104</v>
+        <v>116235504</v>
       </c>
       <c r="B5" t="n">
-        <v>90417</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,14 +1012,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bustadmyren (Bustadmyren), Jmt</t>
+          <t>Bustadmyren, Bustadmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418382</v>
+        <v>418503</v>
       </c>
       <c r="R5" t="n">
-        <v>7014232</v>
+        <v>7014156</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,12 +1082,7 @@
         <v>116234089</v>
       </c>
       <c r="B6" t="n">
-        <v>90759</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1113,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bustadmyren (Bustadmyren), Jmt</t>
+          <t>Bustadmyren, Bustadmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">

--- a/artfynd/A 10491-2024 artfynd.xlsx
+++ b/artfynd/A 10491-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89594008</t>
         </is>
       </c>
     </row>
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116234104</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116235504</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116234089</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>